--- a/new-info26/web.xlsx
+++ b/new-info26/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15960" windowHeight="8235"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="10" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t>domain</t>
   </si>
@@ -41,139 +41,124 @@
     <t>color2</t>
   </si>
   <si>
+    <t>play.fugitive.cloud</t>
+  </si>
+  <si>
+    <t>#a7dbc8</t>
+  </si>
+  <si>
+    <t>sec.fugitive.cloud</t>
+  </si>
+  <si>
+    <t>#fb9966</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>ogees.fun</t>
+  </si>
+  <si>
+    <t>#016a7d</t>
+  </si>
+  <si>
+    <t>newels.fun</t>
+  </si>
+  <si>
+    <t>#e7bf40</t>
+  </si>
+  <si>
+    <t>epicalyxs.fun</t>
+  </si>
+  <si>
+    <t>#36B06F</t>
+  </si>
+  <si>
+    <t>callipyes.com</t>
+  </si>
+  <si>
+    <t>#ff9988</t>
+  </si>
+  <si>
+    <t>epeolatrys.com</t>
+  </si>
+  <si>
+    <t>#30abc5</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>vernations.cloud</t>
+  </si>
+  <si>
+    <t>#ffa500</t>
+  </si>
+  <si>
+    <t>mizars.cloud</t>
+  </si>
+  <si>
+    <t>#9d4edd</t>
+  </si>
+  <si>
+    <t>hortus.cloud</t>
+  </si>
+  <si>
+    <t>#64ffda</t>
+  </si>
+  <si>
+    <t>cruppers.top</t>
+  </si>
+  <si>
+    <t>#e63946</t>
+  </si>
+  <si>
+    <t>secateurs.top</t>
+  </si>
+  <si>
+    <t>#c9a87a</t>
+  </si>
+  <si>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
     <t>rounces.top</t>
   </si>
   <si>
-    <t>#ffa500</t>
-  </si>
-  <si>
-    <t>#bce3fe</t>
+    <t>#92cff4</t>
   </si>
   <si>
     <t>banderole.top</t>
   </si>
   <si>
-    <t>#def0f9</t>
-  </si>
-  <si>
-    <t>#4167b1</t>
+    <t>#ba7ac7</t>
   </si>
   <si>
     <t>peytrels.top</t>
   </si>
   <si>
-    <t>#f8e9a1</t>
-  </si>
-  <si>
-    <t>#d62828</t>
+    <t>#8cd1bc</t>
   </si>
   <si>
     <t>lintels.fun</t>
   </si>
   <si>
-    <t>#f9f0ed</t>
-  </si>
-  <si>
-    <t>#e58889</t>
+    <t>#8bbb6a</t>
   </si>
   <si>
     <t>nargilehs.fun</t>
-  </si>
-  <si>
-    <t>#ebdec6</t>
-  </si>
-  <si>
-    <t>#b57743</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>ogees.fun</t>
-  </si>
-  <si>
-    <t>#016a7d</t>
-  </si>
-  <si>
-    <t>newels.fun</t>
-  </si>
-  <si>
-    <t>#e7bf40</t>
-  </si>
-  <si>
-    <t>epicalyxs.fun</t>
-  </si>
-  <si>
-    <t>#36B06F</t>
-  </si>
-  <si>
-    <t>callipyes.com</t>
-  </si>
-  <si>
-    <t>#ff9988</t>
-  </si>
-  <si>
-    <t>epeolatrys.com</t>
-  </si>
-  <si>
-    <t>#30abc5</t>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>vernations.cloud</t>
-  </si>
-  <si>
-    <t>mizars.cloud</t>
-  </si>
-  <si>
-    <t>#9d4edd</t>
-  </si>
-  <si>
-    <t>hortus.cloud</t>
-  </si>
-  <si>
-    <t>#64ffda</t>
-  </si>
-  <si>
-    <t>cruppers.top</t>
-  </si>
-  <si>
-    <t>#e63946</t>
-  </si>
-  <si>
-    <t>secateurs.top</t>
-  </si>
-  <si>
-    <t>#c9a87a</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>#92cff4</t>
-  </si>
-  <si>
-    <t>#ba7ac7</t>
-  </si>
-  <si>
-    <t>#8cd1bc</t>
-  </si>
-  <si>
-    <t>#8bbb6a</t>
   </si>
 </sst>
 </file>
@@ -186,7 +171,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -224,14 +209,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FFCE9178"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -245,6 +238,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
@@ -400,7 +400,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="57">
+  <fills count="58">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,7 +505,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEF0F9"/>
+        <fgColor rgb="FFA7DBC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFB9966"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -847,28 +853,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -877,122 +874,131 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1036,9 +1042,6 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1054,37 +1057,37 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1488,75 +1491,46 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="20" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="22"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
+      <c r="A3" s="20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="C3" s="24"/>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="rounces.top"/>
-    <hyperlink ref="A3" r:id="rId2" display="banderole.top"/>
-    <hyperlink ref="A4" r:id="rId3" display="peytrels.top"/>
-    <hyperlink ref="A5" r:id="rId4" display="lintels.fun"/>
-    <hyperlink ref="A6" r:id="rId5" display="nargilehs.fun"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1579,18 +1553,18 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>10</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1601,10 +1575,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>12</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1615,10 +1589,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>14</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1629,10 +1603,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1643,10 +1617,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1682,24 +1656,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1710,10 +1684,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="7" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1724,10 +1698,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1738,10 +1712,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1752,10 +1726,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1766,18 +1740,18 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="13" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1811,42 +1785,42 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
